--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487500_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487500_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.811</v>
+        <v>7.7831</v>
       </c>
       <c r="E2" t="n">
-        <v>5.058</v>
+        <v>5.6291</v>
       </c>
       <c r="F2" t="n">
-        <v>1.753</v>
+        <v>2.154</v>
       </c>
       <c r="G2" t="n">
         <v>4.0991</v>
@@ -610,13 +610,13 @@
         <v>2.7419</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.2673</v>
+        <v>0.7047</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.1382</v>
+        <v>0.4329</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.1291</v>
+        <v>0.2719</v>
       </c>
       <c r="V2" t="n">
         <v>1.2166</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.7375</v>
+        <v>4.9449</v>
       </c>
       <c r="E3" t="n">
-        <v>1.9356</v>
+        <v>2.4637</v>
       </c>
       <c r="F3" t="n">
-        <v>2.8019</v>
+        <v>2.4812</v>
       </c>
       <c r="G3" t="n">
         <v>1.8636</v>
@@ -688,13 +688,13 @@
         <v>2.9377</v>
       </c>
       <c r="S3" t="n">
-        <v>0.8313</v>
+        <v>1.0386</v>
       </c>
       <c r="T3" t="n">
-        <v>0.04</v>
+        <v>0.5681</v>
       </c>
       <c r="U3" t="n">
-        <v>0.7913</v>
+        <v>0.4705</v>
       </c>
       <c r="V3" t="n">
         <v>2.0427</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4.1898</v>
+        <v>4.1749</v>
       </c>
       <c r="E4" t="n">
-        <v>2.2071</v>
+        <v>2.3259</v>
       </c>
       <c r="F4" t="n">
-        <v>1.9827</v>
+        <v>1.8491</v>
       </c>
       <c r="G4" t="n">
         <v>0.4349</v>
@@ -766,13 +766,13 @@
         <v>2.1543</v>
       </c>
       <c r="S4" t="n">
-        <v>1.1454</v>
+        <v>1.1305</v>
       </c>
       <c r="T4" t="n">
-        <v>0.5264</v>
+        <v>0.6452</v>
       </c>
       <c r="U4" t="n">
-        <v>0.619</v>
+        <v>0.4854</v>
       </c>
       <c r="V4" t="n">
         <v>1.4344</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3.2395</v>
+        <v>3.4933</v>
       </c>
       <c r="E5" t="n">
-        <v>1.1904</v>
+        <v>1.4709</v>
       </c>
       <c r="F5" t="n">
-        <v>2.0491</v>
+        <v>2.0223</v>
       </c>
       <c r="G5" t="n">
         <v>2.4905</v>
@@ -844,13 +844,13 @@
         <v>2.1543</v>
       </c>
       <c r="S5" t="n">
-        <v>0.6291</v>
+        <v>0.8829</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.3341</v>
+        <v>-0.0535</v>
       </c>
       <c r="U5" t="n">
-        <v>0.9631999999999999</v>
+        <v>0.9365</v>
       </c>
       <c r="V5" t="n">
         <v>1.8825</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>3.1078</v>
+        <v>2.0826</v>
       </c>
       <c r="E6" t="n">
-        <v>1.6131</v>
+        <v>1.0155</v>
       </c>
       <c r="F6" t="n">
-        <v>1.4947</v>
+        <v>1.067</v>
       </c>
       <c r="G6" t="n">
         <v>-1.2165</v>
@@ -922,13 +922,13 @@
         <v>1.5668</v>
       </c>
       <c r="S6" t="n">
-        <v>1.8163</v>
+        <v>0.791</v>
       </c>
       <c r="T6" t="n">
-        <v>0.8057</v>
+        <v>0.2082</v>
       </c>
       <c r="U6" t="n">
-        <v>1.0105</v>
+        <v>0.5828</v>
       </c>
       <c r="V6" t="n">
         <v>0.9412</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.8488</v>
+        <v>0.3476</v>
       </c>
       <c r="E7" t="n">
-        <v>0.6938</v>
+        <v>0.1392</v>
       </c>
       <c r="F7" t="n">
-        <v>0.155</v>
+        <v>0.2084</v>
       </c>
       <c r="G7" t="n">
         <v>-1.2943</v>
@@ -1000,13 +1000,13 @@
         <v>0.7834</v>
       </c>
       <c r="S7" t="n">
-        <v>0.6938</v>
+        <v>0.1926</v>
       </c>
       <c r="T7" t="n">
-        <v>0.9069</v>
+        <v>0.3523</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.2131</v>
+        <v>-0.1597</v>
       </c>
       <c r="V7" t="n">
         <v>0.6659</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>G. GONZALEZ GARCIA</t>
+          <t>S. RODRÍGUEZ TAPIA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.1347</v>
+        <v>-0.5468</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.9751</v>
+        <v>-1.335</v>
       </c>
       <c r="F8" t="n">
-        <v>1.8404</v>
+        <v>0.7882</v>
       </c>
       <c r="G8" t="n">
-        <v>-2.6182</v>
+        <v>-0.4148</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.8555</v>
+        <v>-0.1419</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.7627</v>
+        <v>-0.2729</v>
       </c>
       <c r="J8" t="n">
-        <v>-2.5015</v>
+        <v>-0.621</v>
       </c>
       <c r="K8" t="n">
-        <v>-1.8596</v>
+        <v>0.0612</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.6418</v>
+        <v>-0.6822</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.1167</v>
+        <v>0.2062</v>
       </c>
       <c r="N8" t="n">
-        <v>0.0042</v>
+        <v>-0.2031</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.1209</v>
+        <v>0.4093</v>
       </c>
       <c r="P8" t="n">
-        <v>0.7834</v>
+        <v>-0.1958</v>
       </c>
       <c r="Q8" t="n">
         <v>-0.9792</v>
       </c>
       <c r="R8" t="n">
-        <v>1.7626</v>
+        <v>0.7834</v>
       </c>
       <c r="S8" t="n">
-        <v>1.9754</v>
+        <v>0.0638</v>
       </c>
       <c r="T8" t="n">
-        <v>1.5056</v>
+        <v>0.2652</v>
       </c>
       <c r="U8" t="n">
-        <v>0.4698</v>
+        <v>-0.2014</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.2754</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.2754</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>S. RODRÍGUEZ TAPIA</t>
+          <t>G. GONZALEZ GARCIA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.8003</v>
+        <v>-0.7336</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.642</v>
+        <v>-2.7344</v>
       </c>
       <c r="F9" t="n">
-        <v>0.8417</v>
+        <v>2.0008</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.4148</v>
+        <v>-2.6182</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.1419</v>
+        <v>-1.8555</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.2729</v>
+        <v>-0.7627</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.621</v>
+        <v>-2.5015</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0612</v>
+        <v>-1.8596</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.6822</v>
+        <v>-0.6418</v>
       </c>
       <c r="M9" t="n">
-        <v>0.2062</v>
+        <v>-0.1167</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.2031</v>
+        <v>0.0042</v>
       </c>
       <c r="O9" t="n">
-        <v>0.4093</v>
+        <v>-0.1209</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.1958</v>
+        <v>0.7834</v>
       </c>
       <c r="Q9" t="n">
         <v>-0.9792</v>
       </c>
       <c r="R9" t="n">
-        <v>0.7834</v>
+        <v>1.7626</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.1897</v>
+        <v>1.3765</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.0418</v>
+        <v>0.7463</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.148</v>
+        <v>0.6302</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>-0.2754</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-0.2754</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Y. PINAS</t>
+          <t>N. FUENTES PRADO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.389</v>
+        <v>-1.0747</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.1777</v>
+        <v>-1.4373</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.2113</v>
+        <v>0.3626</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.0275</v>
+        <v>-1.0241</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.0731</v>
+        <v>0.0623</v>
       </c>
       <c r="I10" t="n">
-        <v>0.0456</v>
+        <v>-1.0864</v>
       </c>
       <c r="J10" t="n">
-        <v>0.1017</v>
+        <v>-0.621</v>
       </c>
       <c r="K10" t="n">
         <v>0.0612</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0404</v>
+        <v>-0.6822</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.1292</v>
+        <v>-0.4031</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.1344</v>
+        <v>0.001</v>
       </c>
       <c r="O10" t="n">
-        <v>0.0052</v>
+        <v>-0.4042</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>-0.3917</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>-0.9792</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>0.5875</v>
       </c>
       <c r="S10" t="n">
-        <v>0.1305</v>
+        <v>0.3411</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.2794</v>
+        <v>0.1629</v>
       </c>
       <c r="U10" t="n">
-        <v>0.4099</v>
+        <v>0.1782</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.492</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.492</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>N. FUENTES PRADO</t>
+          <t>Y. PINAS</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.4457</v>
+        <v>-1.1041</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.7014</v>
+        <v>0.027</v>
       </c>
       <c r="F11" t="n">
-        <v>0.2557</v>
+        <v>-1.1311</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.0241</v>
+        <v>-0.0275</v>
       </c>
       <c r="H11" t="n">
-        <v>0.0623</v>
+        <v>-0.0731</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.0864</v>
+        <v>0.0456</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.621</v>
+        <v>0.1017</v>
       </c>
       <c r="K11" t="n">
         <v>0.0612</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.6822</v>
+        <v>0.0404</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.4031</v>
+        <v>-0.1292</v>
       </c>
       <c r="N11" t="n">
-        <v>0.001</v>
+        <v>-0.1344</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.4042</v>
+        <v>0.0052</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.3917</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>-0.9792</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>0.5875</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.0299</v>
+        <v>0.4154</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.1012</v>
+        <v>-0.0747</v>
       </c>
       <c r="U11" t="n">
-        <v>0.0713</v>
+        <v>0.4901</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>-1.492</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>-1.492</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.7469</v>
+        <v>-2.0583</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.6087</v>
+        <v>-2.0805</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.1382</v>
+        <v>0.0222</v>
       </c>
       <c r="G12" t="n">
         <v>-2.9853</v>
@@ -1390,13 +1390,13 @@
         <v>1.1751</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.3859</v>
+        <v>0.3026</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.4993</v>
+        <v>0.0288</v>
       </c>
       <c r="U12" t="n">
-        <v>0.1134</v>
+        <v>0.2738</v>
       </c>
       <c r="V12" t="n">
         <v>-0.5507</v>
@@ -1423,10 +1423,10 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>16.4178</v>
+        <v>17.3089</v>
       </c>
       <c r="E13" t="n">
-        <v>4.593100000000001</v>
+        <v>5.484100000000002</v>
       </c>
       <c r="F13" t="n">
         <v>11.8247</v>
@@ -1441,7 +1441,7 @@
         <v>-4.7758</v>
       </c>
       <c r="J13" t="n">
-        <v>2.9013</v>
+        <v>2.901300000000001</v>
       </c>
       <c r="K13" t="n">
         <v>8.462899999999999</v>
@@ -1456,7 +1456,7 @@
         <v>-4.38</v>
       </c>
       <c r="O13" t="n">
-        <v>0.7859</v>
+        <v>0.7858999999999999</v>
       </c>
       <c r="P13" t="n">
         <v>4.8963</v>
@@ -1468,13 +1468,13 @@
         <v>16.647</v>
       </c>
       <c r="S13" t="n">
-        <v>6.348999999999999</v>
+        <v>7.2397</v>
       </c>
       <c r="T13" t="n">
-        <v>2.390600000000001</v>
+        <v>3.2817</v>
       </c>
       <c r="U13" t="n">
-        <v>3.958199999999999</v>
+        <v>3.958299999999999</v>
       </c>
       <c r="V13" t="n">
         <v>5.8652</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>D. LASTRA GONZALEZ</t>
+          <t>J. GONZALEZ DACAL</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>0.0402</v>
+        <v>0.8257</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.4938</v>
+        <v>0.5563</v>
       </c>
       <c r="F14" t="n">
-        <v>0.534</v>
+        <v>0.2694</v>
       </c>
       <c r="G14" t="n">
-        <v>0.521</v>
+        <v>-0.6881</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.2977</v>
+        <v>0.1406</v>
       </c>
       <c r="I14" t="n">
-        <v>0.8187</v>
+        <v>-0.8287</v>
       </c>
       <c r="J14" t="n">
-        <v>0.0408</v>
+        <v>-0.2401</v>
       </c>
       <c r="K14" t="n">
-        <v>0.0408</v>
+        <v>1.1551</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>-1.3952</v>
       </c>
       <c r="M14" t="n">
-        <v>0.4802</v>
+        <v>-0.448</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.3385</v>
+        <v>-1.0145</v>
       </c>
       <c r="O14" t="n">
-        <v>0.8187</v>
+        <v>0.5666</v>
       </c>
       <c r="P14" t="n">
         <v>0.3917</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>-0.9792</v>
       </c>
       <c r="R14" t="n">
-        <v>0.3917</v>
+        <v>1.3709</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.8725000000000001</v>
+        <v>-0.4274</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.5346</v>
+        <v>-0.6575</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.3379</v>
+        <v>0.2301</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>1.5495</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>2.4332</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>-0.8837</v>
       </c>
     </row>
     <row r="15">
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.1088</v>
+        <v>0.577</v>
       </c>
       <c r="E15" t="n">
-        <v>-1.5113</v>
+        <v>-1.7159</v>
       </c>
       <c r="F15" t="n">
-        <v>1.4025</v>
+        <v>2.293</v>
       </c>
       <c r="G15" t="n">
         <v>1.7167</v>
@@ -1624,13 +1624,13 @@
         <v>2.1543</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.4131</v>
+        <v>-0.7272</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.7081</v>
+        <v>-0.9127999999999999</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.7049</v>
+        <v>0.1856</v>
       </c>
       <c r="V15" t="n">
         <v>-0.6083</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>R. BLANCO CARBALLO</t>
+          <t>D. LASTRA GONZALEZ</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,58 +1657,58 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.2042</v>
+        <v>0.4467</v>
       </c>
       <c r="E16" t="n">
-        <v>0</v>
+        <v>-0.4938</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.2042</v>
+        <v>0.9405</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.2042</v>
+        <v>0.521</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.2042</v>
+        <v>-0.2977</v>
       </c>
       <c r="I16" t="n">
-        <v>0</v>
+        <v>0.8187</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>0.0408</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>0.0408</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.2042</v>
+        <v>0.4802</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.2042</v>
+        <v>-0.3385</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>0.8187</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>0.3917</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>0.3917</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>-0.466</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>-0.5346</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>0.0687</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>J. GONZALEZ DACAL</t>
+          <t>J. PRIETO LORIENTE</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.5212</v>
+        <v>0.1192</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.0577</v>
+        <v>1.731</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.4635</v>
+        <v>-1.6118</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.6881</v>
+        <v>3.3801</v>
       </c>
       <c r="H17" t="n">
-        <v>0.1406</v>
+        <v>-1.5709</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.8287</v>
+        <v>4.951</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.2401</v>
+        <v>4.7176</v>
       </c>
       <c r="K17" t="n">
-        <v>1.1551</v>
+        <v>0.4643</v>
       </c>
       <c r="L17" t="n">
-        <v>-1.3952</v>
+        <v>4.2532</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.448</v>
+        <v>-1.3375</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.0145</v>
+        <v>-2.0353</v>
       </c>
       <c r="O17" t="n">
-        <v>0.5666</v>
+        <v>0.6978</v>
       </c>
       <c r="P17" t="n">
-        <v>0.3917</v>
+        <v>-1.9585</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.9792</v>
+        <v>-3.917</v>
       </c>
       <c r="R17" t="n">
-        <v>1.3709</v>
+        <v>1.9585</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.7743</v>
+        <v>-0.6365</v>
       </c>
       <c r="T17" t="n">
-        <v>-1.2716</v>
+        <v>-0.8369</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.5028</v>
+        <v>0.2004</v>
       </c>
       <c r="V17" t="n">
-        <v>1.5495</v>
+        <v>-0.6659</v>
       </c>
       <c r="W17" t="n">
-        <v>2.4332</v>
+        <v>1.7673</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.8837</v>
+        <v>-2.4332</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>J. PRIETO LORIENTE</t>
+          <t>R. BLANCO CARBALLO</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.0719</v>
+        <v>-0.2042</v>
       </c>
       <c r="E18" t="n">
-        <v>1.2193</v>
+        <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>-2.2912</v>
+        <v>-0.2042</v>
       </c>
       <c r="G18" t="n">
-        <v>3.3801</v>
+        <v>-0.2042</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.5709</v>
+        <v>-0.2042</v>
       </c>
       <c r="I18" t="n">
-        <v>4.951</v>
+        <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>4.7176</v>
+        <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>0.4643</v>
+        <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>4.2532</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.3375</v>
+        <v>-0.2042</v>
       </c>
       <c r="N18" t="n">
-        <v>-2.0353</v>
+        <v>-0.2042</v>
       </c>
       <c r="O18" t="n">
-        <v>0.6978</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>-1.9585</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>-3.917</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.9585</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.8276</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>-1.3486</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.479</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.6659</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>1.7673</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-2.4332</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>P. NJIE</t>
+          <t>D. REIRIZ MENDEZ</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.35</v>
+        <v>-1.3623</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.8481</v>
+        <v>-0.9209000000000001</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.5019</v>
+        <v>-0.4414</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.6489</v>
+        <v>-1.7776</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.7557</v>
+        <v>0.3039</v>
       </c>
       <c r="I19" t="n">
-        <v>1.1068</v>
+        <v>-2.0816</v>
       </c>
       <c r="J19" t="n">
-        <v>0.425</v>
+        <v>-1.1203</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.2621</v>
+        <v>0.1633</v>
       </c>
       <c r="L19" t="n">
-        <v>0.6871</v>
+        <v>-1.2836</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.0739</v>
+        <v>-0.6573</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.4936</v>
+        <v>0.1406</v>
       </c>
       <c r="O19" t="n">
-        <v>0.4197</v>
+        <v>-0.7979000000000001</v>
       </c>
       <c r="P19" t="n">
-        <v>-2.3502</v>
+        <v>0.7834</v>
       </c>
       <c r="Q19" t="n">
-        <v>-3.917</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.5668</v>
+        <v>0.7834</v>
       </c>
       <c r="S19" t="n">
-        <v>1.9821</v>
+        <v>0.1826</v>
       </c>
       <c r="T19" t="n">
-        <v>2.0932</v>
+        <v>0.1994</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.1111</v>
+        <v>-0.0168</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.3329</v>
+        <v>-0.5507</v>
       </c>
       <c r="W19" t="n">
-        <v>0.5507</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.8837</v>
+        <v>-0.5507</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>D. REIRIZ MENDEZ</t>
+          <t>P. NJIE</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.4499</v>
+        <v>-2.6185</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.8186</v>
+        <v>-2.1785</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.6313</v>
+        <v>-0.44</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.7776</v>
+        <v>-0.6489</v>
       </c>
       <c r="H20" t="n">
-        <v>0.3039</v>
+        <v>-1.7557</v>
       </c>
       <c r="I20" t="n">
-        <v>-2.0816</v>
+        <v>1.1068</v>
       </c>
       <c r="J20" t="n">
-        <v>-1.1203</v>
+        <v>0.425</v>
       </c>
       <c r="K20" t="n">
-        <v>0.1633</v>
+        <v>-0.2621</v>
       </c>
       <c r="L20" t="n">
-        <v>-1.2836</v>
+        <v>0.6871</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.6573</v>
+        <v>-1.0739</v>
       </c>
       <c r="N20" t="n">
-        <v>0.1406</v>
+        <v>-1.4936</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.7979000000000001</v>
+        <v>0.4197</v>
       </c>
       <c r="P20" t="n">
-        <v>0.7834</v>
+        <v>-2.3502</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-3.917</v>
       </c>
       <c r="R20" t="n">
-        <v>0.7834</v>
+        <v>1.5668</v>
       </c>
       <c r="S20" t="n">
-        <v>0.095</v>
+        <v>0.7136</v>
       </c>
       <c r="T20" t="n">
-        <v>0.3017</v>
+        <v>0.7628</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.2067</v>
+        <v>-0.0493</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.5507</v>
+        <v>-0.3329</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>0.5507</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.5507</v>
+        <v>-0.8837</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.323</v>
+        <v>-2.959</v>
       </c>
       <c r="E21" t="n">
         <v>-3.8995</v>
       </c>
       <c r="F21" t="n">
-        <v>1.5765</v>
+        <v>0.9406</v>
       </c>
       <c r="G21" t="n">
         <v>0.2583</v>
@@ -2092,13 +2092,13 @@
         <v>0.7834</v>
       </c>
       <c r="S21" t="n">
-        <v>0.4763</v>
+        <v>-0.1597</v>
       </c>
       <c r="T21" t="n">
         <v>-1.111</v>
       </c>
       <c r="U21" t="n">
-        <v>1.5873</v>
+        <v>0.9513</v>
       </c>
       <c r="V21" t="n">
         <v>-1.8825</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.9934</v>
+        <v>-3.2992</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.0803</v>
+        <v>-0.8757</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.9131</v>
+        <v>-2.4236</v>
       </c>
       <c r="G22" t="n">
         <v>0.5205</v>
@@ -2170,13 +2170,13 @@
         <v>1.7626</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.181</v>
+        <v>-0.4868</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.4882</v>
+        <v>-0.2835</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.6929</v>
+        <v>-0.2033</v>
       </c>
       <c r="V22" t="n">
         <v>-2.1578</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-5.4356</v>
+        <v>-4.5321</v>
       </c>
       <c r="E23" t="n">
-        <v>-4.3347</v>
+        <v>-4.0276</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.1009</v>
+        <v>-0.5044999999999999</v>
       </c>
       <c r="G23" t="n">
         <v>-2.3852</v>
@@ -2248,13 +2248,13 @@
         <v>0.9792</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.8337</v>
+        <v>-0.9303</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.891</v>
+        <v>-0.584</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.9427</v>
+        <v>-0.3463</v>
       </c>
       <c r="V23" t="n">
         <v>-1.2166</v>
@@ -2281,16 +2281,16 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-16.4178</v>
+        <v>-13.0067</v>
       </c>
       <c r="E24" t="n">
-        <v>-11.8247</v>
+        <v>-11.8246</v>
       </c>
       <c r="F24" t="n">
-        <v>-4.5931</v>
+        <v>-1.182</v>
       </c>
       <c r="G24" t="n">
-        <v>0.6925999999999997</v>
+        <v>0.6926000000000005</v>
       </c>
       <c r="H24" t="n">
         <v>-4.0831</v>
@@ -2305,7 +2305,7 @@
         <v>4.3798</v>
       </c>
       <c r="L24" t="n">
-        <v>-0.7860000000000003</v>
+        <v>-0.7860000000000005</v>
       </c>
       <c r="M24" t="n">
         <v>-2.9013</v>
@@ -2326,13 +2326,13 @@
         <v>11.7508</v>
       </c>
       <c r="S24" t="n">
-        <v>-6.348800000000001</v>
+        <v>-2.9377</v>
       </c>
       <c r="T24" t="n">
-        <v>-3.9582</v>
+        <v>-3.9581</v>
       </c>
       <c r="U24" t="n">
-        <v>-2.3907</v>
+        <v>1.0204</v>
       </c>
       <c r="V24" t="n">
         <v>-5.8652</v>
